--- a/artfynd/A 18790-2026 artfynd.xlsx
+++ b/artfynd/A 18790-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60469528</v>
+        <v>71997839</v>
       </c>
       <c r="B2" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,36 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>300m SO  vägen mot Skålgrund, Upl</t>
+          <t>Torsätra 1,5 km NV, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654978.3457285777</v>
+        <v>655081</v>
       </c>
       <c r="R2" t="n">
-        <v>6608313.70022771</v>
+        <v>6608210</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-06-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flera exemplar lite här och där i dikena.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,33 +767,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Grönlund</t>
+          <t>Linda Irebrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Grönlund</t>
+          <t>Linda Irebrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71997839</v>
+        <v>60469528</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,45 +797,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>223597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Torsätra 1,5 km NV, Upl</t>
+          <t>300m SO  vägen mot Skålgrund, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655081.1734043534</v>
+        <v>654978</v>
       </c>
       <c r="R3" t="n">
-        <v>6608209.951574639</v>
+        <v>6608314</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,27 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera exemplar lite här och där i dikena.</t>
+          <t>2016-07-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,19 +864,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linda Irebrand</t>
+          <t>Eva Grönlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linda Irebrand</t>
+          <t>Eva Grönlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
